--- a/new-stats/gwangju-fc.xlsx
+++ b/new-stats/gwangju-fc.xlsx
@@ -2131,40 +2131,112 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ulsan HD</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>13</v>
+      </c>
+      <c r="N32" t="n">
+        <v>11</v>
+      </c>
+      <c r="O32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P32" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Daejeon</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>16</v>
+      </c>
+      <c r="N33" t="n">
+        <v>24</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/gwangju-fc.xlsx
+++ b/new-stats/gwangju-fc.xlsx
@@ -2239,22 +2239,58 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bucheon</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>9</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
